--- a/research/GPT.AX/Reports/GPT.AX_DCF_Model.xlsx
+++ b/research/GPT.AX/Reports/GPT.AX_DCF_Model.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="170">
   <si>
     <t xml:space="preserve">Ticker</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Model</t>
   </si>
   <si>
-    <t xml:space="preserve">owner_fcf_dcf_component</t>
+    <t xml:space="preserve">REIT AFFO capitalisation at cost of equity (engine route)</t>
   </si>
   <si>
     <t xml:space="preserve">Currency (model)</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Built at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-22T11:55:23Z</t>
+    <t xml:space="preserve">2026-09-22T20:11:22Z</t>
   </si>
   <si>
     <t xml:space="preserve">Drivers file</t>
@@ -236,6 +236,15 @@
   </si>
   <si>
     <t xml:space="preserve">Occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFOPerSecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetGearing</t>
   </si>
   <si>
     <t xml:space="preserve">FY2019</t>
@@ -1014,7 +1023,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1120,10 +1129,19 @@
       <c r="AH1" s="2" t="s">
         <v>68</v>
       </c>
+      <c r="AI1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>807</v>
@@ -1179,10 +1197,19 @@
       <c r="AG2" s="0" t="n">
         <v>5.8</v>
       </c>
+      <c r="AI2" s="0" t="n">
+        <v>613.7</v>
+      </c>
+      <c r="AJ2" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="AK2" s="0" t="n">
+        <v>22.1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>716.7</v>
@@ -1238,10 +1265,19 @@
       <c r="AG3" s="0" t="n">
         <v>5.57</v>
       </c>
+      <c r="AI3" s="0" t="n">
+        <v>554.7</v>
+      </c>
+      <c r="AJ3" s="0" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="AK3" s="0" t="n">
+        <v>23.2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>795.2</v>
@@ -1297,10 +1333,19 @@
       <c r="AG4" s="0" t="n">
         <v>6.09</v>
       </c>
+      <c r="AI4" s="0" t="n">
+        <v>554.5</v>
+      </c>
+      <c r="AJ4" s="0" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="AK4" s="0" t="n">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>815.5</v>
@@ -1356,10 +1401,16 @@
       <c r="AG5" s="0" t="n">
         <v>5.98</v>
       </c>
+      <c r="AI5" s="0" t="n">
+        <v>620.6</v>
+      </c>
+      <c r="AK5" s="0" t="n">
+        <v>28.5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>902.6</v>
@@ -1418,10 +1469,19 @@
       <c r="AH6" s="0" t="n">
         <v>98.2</v>
       </c>
+      <c r="AI6" s="0" t="n">
+        <v>600.9</v>
+      </c>
+      <c r="AJ6" s="0" t="n">
+        <v>31.37</v>
+      </c>
+      <c r="AK6" s="0" t="n">
+        <v>28.3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>988.7</v>
@@ -1480,10 +1540,19 @@
       <c r="AG7" s="0" t="n">
         <v>5.27</v>
       </c>
+      <c r="AI7" s="0" t="n">
+        <v>616.3</v>
+      </c>
+      <c r="AJ7" s="0" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="AK7" s="0" t="n">
+        <v>26.5</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>1031.9</v>
@@ -1547,6 +1616,15 @@
       </c>
       <c r="AH8" s="0" t="n">
         <v>97.6</v>
+      </c>
+      <c r="AI8" s="0" t="n">
+        <v>650.5</v>
+      </c>
+      <c r="AJ8" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK8" s="0" t="n">
+        <v>31.1</v>
       </c>
     </row>
   </sheetData>
@@ -1573,15 +1651,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>4.51</v>
@@ -1589,7 +1667,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>1918.3</v>
@@ -1597,7 +1675,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
@@ -1605,7 +1683,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
@@ -1613,7 +1691,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>15</v>
@@ -1621,7 +1699,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>1031.9</v>
@@ -1629,23 +1707,23 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
@@ -1653,42 +1731,42 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>3</v>
@@ -1723,7 +1801,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>62.5</v>
@@ -1758,7 +1836,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -1793,7 +1871,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -1828,7 +1906,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -1863,7 +1941,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>15.5</v>
@@ -1898,7 +1976,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>0</v>
@@ -1933,7 +2011,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>9</v>
@@ -1941,7 +2019,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>1.5</v>
@@ -1949,7 +2027,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>14</v>
@@ -1957,7 +2035,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
@@ -1965,7 +2043,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0.25</v>
@@ -1973,42 +2051,42 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>4</v>
@@ -2043,7 +2121,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>63</v>
@@ -2078,7 +2156,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0</v>
@@ -2113,7 +2191,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>0</v>
@@ -2148,7 +2226,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0</v>
@@ -2183,7 +2261,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>15.3</v>
@@ -2218,7 +2296,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>0</v>
@@ -2253,7 +2331,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>9</v>
@@ -2261,7 +2339,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>2.5</v>
@@ -2269,7 +2347,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>18</v>
@@ -2277,7 +2355,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
@@ -2285,7 +2363,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0.5</v>
@@ -2293,42 +2371,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>5.5</v>
@@ -2363,7 +2441,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>63.2</v>
@@ -2398,7 +2476,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -2433,7 +2511,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -2468,7 +2546,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -2503,7 +2581,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>15</v>
@@ -2538,7 +2616,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -2573,7 +2651,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B48" s="3" t="n">
         <v>9</v>
@@ -2581,7 +2659,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B49" s="3" t="n">
         <v>3</v>
@@ -2589,7 +2667,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>18</v>
@@ -2597,7 +2675,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B51" s="3" t="n">
         <v>0</v>
@@ -2605,7 +2683,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B52" s="3" t="n">
         <v>0.25</v>
@@ -2635,50 +2713,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -2726,7 +2804,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C13</f>
@@ -2819,7 +2897,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C14</f>
@@ -2909,7 +2987,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C15</f>
@@ -2954,7 +3032,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
@@ -2999,7 +3077,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
@@ -3044,7 +3122,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C17/100</f>
@@ -3089,7 +3167,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
@@ -3134,7 +3212,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C19</f>
@@ -3179,7 +3257,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
@@ -3224,7 +3302,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
@@ -3269,7 +3347,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C18/100</f>
@@ -3314,7 +3392,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$23/100</f>
@@ -3359,7 +3437,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
@@ -3404,7 +3482,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -3449,7 +3527,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
@@ -3494,7 +3572,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C16</f>
@@ -3539,7 +3617,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -3584,12 +3662,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$20</f>
@@ -3598,7 +3676,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$21</f>
@@ -3607,7 +3685,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$22</f>
@@ -3616,7 +3694,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
@@ -3625,7 +3703,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
@@ -3634,7 +3712,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
@@ -3643,7 +3721,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
@@ -3652,7 +3730,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
@@ -3661,7 +3739,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
@@ -3670,7 +3748,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
@@ -3679,7 +3757,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
@@ -3688,7 +3766,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -3697,7 +3775,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
@@ -3706,7 +3784,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
@@ -3715,7 +3793,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
@@ -3724,7 +3802,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -3733,7 +3811,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -3742,7 +3820,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
@@ -3751,7 +3829,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -3782,50 +3860,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -3873,7 +3951,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C27</f>
@@ -3966,7 +4044,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C28</f>
@@ -4056,7 +4134,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C29</f>
@@ -4101,7 +4179,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
@@ -4146,7 +4224,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
@@ -4191,7 +4269,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C31/100</f>
@@ -4236,7 +4314,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
@@ -4281,7 +4359,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C33</f>
@@ -4326,7 +4404,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
@@ -4371,7 +4449,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
@@ -4416,7 +4494,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C32/100</f>
@@ -4461,7 +4539,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$37/100</f>
@@ -4506,7 +4584,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
@@ -4551,7 +4629,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -4596,7 +4674,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
@@ -4641,7 +4719,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C30</f>
@@ -4686,7 +4764,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -4731,12 +4809,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$34</f>
@@ -4745,7 +4823,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$35</f>
@@ -4754,7 +4832,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$36</f>
@@ -4763,7 +4841,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
@@ -4772,7 +4850,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
@@ -4781,7 +4859,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
@@ -4790,7 +4868,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
@@ -4799,7 +4877,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
@@ -4808,7 +4886,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
@@ -4817,7 +4895,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
@@ -4826,7 +4904,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
@@ -4835,7 +4913,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -4844,7 +4922,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
@@ -4853,7 +4931,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
@@ -4862,7 +4940,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
@@ -4871,7 +4949,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -4880,7 +4958,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -4889,7 +4967,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
@@ -4898,7 +4976,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -4929,50 +5007,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0</v>
@@ -5020,7 +5098,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Assumptions!C41</f>
@@ -5113,7 +5191,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Assumptions!C42</f>
@@ -5203,7 +5281,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">Assumptions!C43</f>
@@ -5248,7 +5326,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C10" s="0" t="n">
         <f aca="false">-C6*C9/100</f>
@@ -5293,7 +5371,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">C8+C10+C24</f>
@@ -5338,7 +5416,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">-C6*Assumptions!C45/100</f>
@@ -5383,7 +5461,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C13" s="0" t="n">
         <f aca="false">C11+C12</f>
@@ -5428,7 +5506,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Assumptions!C47</f>
@@ -5473,7 +5551,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C15" s="0" t="n">
         <f aca="false">C13-MAX(0,C13)*C14/100</f>
@@ -5518,7 +5596,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C16" s="0" t="n">
         <f aca="false">-C12</f>
@@ -5563,7 +5641,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="n">
         <f aca="false">-C6*Assumptions!C46/100</f>
@@ -5608,7 +5686,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="n">
         <f aca="false">(C6-B6)*Assumptions!$B$51/100</f>
@@ -5653,7 +5731,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C19" s="0" t="n">
         <f aca="false">C15+C16+C17+C18</f>
@@ -5698,7 +5776,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C20" s="0" t="n">
         <f aca="false">1/(1+$B$27/100)^C4</f>
@@ -5743,7 +5821,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C21" s="0" t="n">
         <f aca="false">C19*C20</f>
@@ -5788,7 +5866,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4" t="n">
         <f aca="false">Assumptions!C44</f>
@@ -5833,7 +5911,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C24" s="0" t="n">
         <f aca="false">-C6*C23/100</f>
@@ -5878,12 +5956,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B27" s="4" t="n">
         <f aca="false">Assumptions!$B$48</f>
@@ -5892,7 +5970,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B28" s="4" t="n">
         <f aca="false">Assumptions!$B$49</f>
@@ -5901,7 +5979,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B29" s="4" t="n">
         <f aca="false">Assumptions!$B$50</f>
@@ -5910,7 +5988,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">SUM(C21:L21)</f>
@@ -5919,7 +5997,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B31" s="0" t="n">
         <f aca="false">L19</f>
@@ -5928,7 +6006,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,B31*(1+B28/100)/((B27-B28)/100),B31*B29)</f>
@@ -5937,7 +6015,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">B31*B29</f>
@@ -5946,7 +6024,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">MAX(0,MIN(B32,B33))</f>
@@ -5955,7 +6033,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">B34/(1+B27/100)^L4</f>
@@ -5964,7 +6042,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">B30+B35</f>
@@ -5973,7 +6051,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B37" s="0" t="n">
         <f aca="false">B36+Assumptions!$B$5-Assumptions!$B$4</f>
@@ -5982,7 +6060,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B38" s="0" t="n">
         <f aca="false">B37/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -5991,7 +6069,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B39" s="4" t="n">
         <f aca="false">B38/Assumptions!$B$2-1</f>
@@ -6000,7 +6078,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B41" s="0" t="n">
         <f aca="false">SUMPRODUCT(-C10:L10/(1+$B$27/100)^C4:L4)</f>
@@ -6009,7 +6087,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B42" s="0" t="n">
         <f aca="false">IF(B27&gt;B28,-L10*(1+B28/100)/((B27-B28)/100),-L10*20)/(1+B27/100)^L4</f>
@@ -6018,7 +6096,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B43" s="0" t="n">
         <f aca="false">(B37+B41+B42)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6027,7 +6105,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B45" s="4" t="n">
         <f aca="false">Assumptions!$B$6</f>
@@ -6036,7 +6114,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">MAX(0,MIN(IF(B45&gt;B28,B31*(1+B28/100)/((B45-B28)/100),B31*B29),B31*B29))</f>
@@ -6045,7 +6123,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">(SUMPRODUCT(C19:L19/(1+B45/100)^C4:L4)+B46/(1+B45/100)^L4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6076,32 +6154,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B4" s="4" t="n">
         <f aca="false">DCF_Bear!$B$38</f>
@@ -6126,7 +6204,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B5" s="4" t="n">
         <f aca="false">DCF_Base!$B$38</f>
@@ -6151,7 +6229,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">DCF_Bull!$B$38</f>
@@ -6176,7 +6254,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">SUMPRODUCT(B4:B6,D4:D6)</f>
@@ -6185,7 +6263,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">SUMPRODUCT(E4:E6,D4:D6)</f>
@@ -6194,7 +6272,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">1-Assumptions!$B$2/B8</f>
@@ -6203,7 +6281,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B11" s="0" t="str">
         <f aca="false">IF(ABS(B9-B8)&gt;0.01*ABS(B8),(Assumptions!$B$2-B8)/(B9-B8)*100,"n/a")</f>
@@ -6212,7 +6290,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">SUMPRODUCT(F4:F6,D4:D6)</f>
@@ -6221,15 +6299,15 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$15/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$15&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$15-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$15/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6241,7 +6319,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$16/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$16&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$16-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$16/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6253,7 +6331,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$17/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$17&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$17-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$17/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6265,7 +6343,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$18/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$18&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$18-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$18/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6277,7 +6355,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">(SUMPRODUCT(DCF_Base!$C$19:$L$19/(1+$C$19/100)^DCF_Base!$C$4:$L$4)+MAX(0,MIN(IF($C$19&gt;DCF_Base!$B$28,DCF_Base!$L$19*(1+DCF_Base!$B$28/100)/(($C$19-DCF_Base!$B$28)/100),DCF_Base!$L$19*DCF_Base!$B$29),DCF_Base!$L$19*DCF_Base!$B$29))/(1+$C$19/100)^DCF_Base!$L$4+Assumptions!$B$5-Assumptions!$B$4)/Assumptions!$B$3*Assumptions!$B$10</f>
@@ -6289,7 +6367,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
